--- a/Compititor's_Price/Celotex_Prices/Celotex_Prices_10-06-2025.xlsx
+++ b/Compititor's_Price/Celotex_Prices/Celotex_Prices_10-06-2025.xlsx
@@ -1217,12 +1217,12 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>£26.87</t>
+          <t>£26.78</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>£26.87</t>
+          <t>£26.78</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -1411,12 +1411,12 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>£29.42</t>
+          <t>£29.25</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>£29.42</t>
+          <t>£29.25</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -1508,12 +1508,12 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>£37.00</t>
+          <t>£36.90</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>£37.00</t>
+          <t>£36.90</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -1702,12 +1702,12 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>£42.90</t>
+          <t>£42.78</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>£42.90</t>
+          <t>£42.78</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
@@ -1896,12 +1896,12 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>£44.64</t>
+          <t>£43.58</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>£44.64</t>
+          <t>£43.58</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
@@ -2038,7 +2038,7 @@
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>£734.81</t>
+          <t>£729.17</t>
         </is>
       </c>
       <c r="M17" t="inlineStr">
